--- a/feedback_surveys/012_mobile_app_customer_experience_survey_form--feedback_surveys.xlsx
+++ b/feedback_surveys/012_mobile_app_customer_experience_survey_form--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'social_media',_'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'social_media', 'value': 'social_media'}</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'online_search',_'value':_'online_search'}</t>
+          <t>online_search</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'online_search', 'value': 'online_search'}</t>
+          <t>online search</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'word_of_mouth',_'value':_'word_of_mouth'}</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'word_of_mouth', 'value': 'word_of_mouth'}</t>
+          <t>word of mouth</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'design',_'value':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'design', 'value': 'design'}</t>
+          <t>design</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'features',_'value':_'features'}</t>
+          <t>features</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'features', 'value': 'features'}</t>
+          <t>features</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'overall_experience',_'value':_'overall_experience'}</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'overall_experience', 'value': 'overall_experience'}</t>
+          <t>overall experience</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maybe',_'value':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maybe', 'value': 'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'before',_'value':_'before'}</t>
+          <t>before</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'before', 'value': 'before'}</t>
+          <t>before</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'after',_'value':_'after'}</t>
+          <t>after</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'after', 'value': 'after'}</t>
+          <t>after</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'never', 'value': 'never'}</t>
+          <t>never</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'less_than_15',_'value':_'less_than_15'}</t>
+          <t>less_than_15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'less_than_15', 'value': 'less_than_15'}</t>
+          <t>less than 15</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'more_than_15',_'value':_'more_than_15'}</t>
+          <t>more_than_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'more_than_15', 'value': 'more_than_15'}</t>
+          <t>more than 15</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maybe',_'value':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maybe', 'value': 'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'feature_1',_'value':_'feature_1'}</t>
+          <t>feature_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'feature_1', 'value': 'feature_1'}</t>
+          <t>feature 1</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'feature_2',_'value':_'feature_2'}</t>
+          <t>feature_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'feature_2', 'value': 'feature_2'}</t>
+          <t>feature 2</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'feature_3',_'value':_'feature_3'}</t>
+          <t>feature_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'feature_3', 'value': 'feature_3'}</t>
+          <t>feature 3</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'feature_4',_'value':_'feature_4'}</t>
+          <t>feature_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'feature_4', 'value': 'feature_4'}</t>
+          <t>feature 4</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'feature_5',_'value':_'feature_5'}</t>
+          <t>feature_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'feature_5', 'value': 'feature_5'}</t>
+          <t>feature 5</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'one',_'value':_'one',_'required':_true}</t>
+          <t>one</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'one', 'value': 'one', 'required': True}</t>
+          <t>one</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'two',_'value':_'two'}</t>
+          <t>two</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'two', 'value': 'two'}</t>
+          <t>two</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'three',_'value':_'three'}</t>
+          <t>three</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'three', 'value': 'three'}</t>
+          <t>three</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maybe',_'value':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maybe', 'value': 'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maybe',_'value':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maybe', 'value': 'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'scale_1',_'value':_'scale_1'}</t>
+          <t>scale_1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'scale_1', 'value': 'scale_1'}</t>
+          <t>scale 1</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'scale_2',_'value':_'scale_2'}</t>
+          <t>scale_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'scale_2', 'value': 'scale_2'}</t>
+          <t>scale 2</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'scale_3',_'value':_'scale_3'}</t>
+          <t>scale_3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'scale_3', 'value': 'scale_3'}</t>
+          <t>scale 3</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'scale_4',_'value':_'scale_4'}</t>
+          <t>scale_4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'scale_4', 'value': 'scale_4'}</t>
+          <t>scale 4</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'scale_5',_'value':_'scale_5'}</t>
+          <t>scale_5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'scale_5', 'value': 'scale_5'}</t>
+          <t>scale 5</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maybe',_'value':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maybe', 'value': 'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maybe',_'value':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'maybe', 'value': 'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
     </row>
